--- a/clustering/8 subclusters (factoriescap_s (costs) 0).xlsx
+++ b/clustering/8 subclusters (factoriescap_s (costs) 0).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12885"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12885"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -81,6 +81,8 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="11"/>

--- a/clustering/8 subclusters (factoriescap_s (costs) 0).xlsx
+++ b/clustering/8 subclusters (factoriescap_s (costs) 0).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12885"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12885"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -902,6 +902,42 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B9">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C9">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D9">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E9">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -913,7 +949,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C9">
+  <conditionalFormatting sqref="B13:B20">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -925,7 +961,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D9">
+  <conditionalFormatting sqref="C24:E24">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -937,7 +973,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E9">
+  <conditionalFormatting sqref="C26:E26">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -949,7 +985,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B13:B20">
+  <conditionalFormatting sqref="C30:E30">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>

--- a/clustering/8 subclusters (factoriescap_s (costs) 0).xlsx
+++ b/clustering/8 subclusters (factoriescap_s (costs) 0).xlsx
@@ -693,11 +693,11 @@
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="5">
-        <f t="shared" ref="C16:E16" si="2">C5/$B5</f>
+        <f>C5/$B5</f>
         <v>2.7122711077277686E-3</v>
       </c>
       <c r="D16" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="C16:E16" si="2">D5/$B5</f>
         <v>3.7192729789686357E-4</v>
       </c>
       <c r="E16" s="5">
@@ -961,42 +961,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C24:E24">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C26:E26">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C30:E30">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/clustering/8 subclusters (factoriescap_s (costs) 0).xlsx
+++ b/clustering/8 subclusters (factoriescap_s (costs) 0).xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="14">
   <si>
     <t>clust</t>
   </si>
@@ -58,6 +58,9 @@
   </si>
   <si>
     <t>3 (upper)</t>
+  </si>
+  <si>
+    <t>Медианы кластеров</t>
   </si>
 </sst>
 </file>
@@ -69,7 +72,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.00_ ;\-#,##0.00\ "/>
     <numFmt numFmtId="165" formatCode="0.0000%"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -90,6 +93,20 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -129,7 +146,7 @@
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -146,6 +163,10 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -450,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.42578125" customWidth="1"/>
@@ -697,7 +718,7 @@
         <v>2.7122711077277686E-3</v>
       </c>
       <c r="D16" s="5">
-        <f t="shared" ref="C16:E16" si="2">D5/$B5</f>
+        <f t="shared" ref="D16:E16" si="2">D5/$B5</f>
         <v>3.7192729789686357E-4</v>
       </c>
       <c r="E16" s="5">
@@ -900,8 +921,146 @@
         <v>1.5716255668929728</v>
       </c>
     </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <v>0</v>
+      </c>
+      <c r="B34" s="3">
+        <v>1783343.4999999951</v>
+      </c>
+      <c r="C34" s="3">
+        <v>4252.4216107599877</v>
+      </c>
+      <c r="D34" s="3">
+        <v>13.552200919999899</v>
+      </c>
+      <c r="E34" s="3">
+        <v>6.3405810799994908</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
+        <v>1</v>
+      </c>
+      <c r="B35" s="3">
+        <v>13858386.5</v>
+      </c>
+      <c r="C35" s="3">
+        <v>33565.597076099992</v>
+      </c>
+      <c r="D35" s="3">
+        <v>5021.2710237600004</v>
+      </c>
+      <c r="E35" s="3">
+        <v>9.3762416399997388</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
+        <v>2</v>
+      </c>
+      <c r="B36" s="3">
+        <v>12161153.999999991</v>
+      </c>
+      <c r="C36" s="3">
+        <v>35568.661953510004</v>
+      </c>
+      <c r="D36" s="3">
+        <v>592.13074661999974</v>
+      </c>
+      <c r="E36" s="3">
+        <v>6413.5022275799993</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
+        <v>3</v>
+      </c>
+      <c r="B37" s="3">
+        <v>66796992</v>
+      </c>
+      <c r="C37" s="3">
+        <v>220411.94692799999</v>
+      </c>
+      <c r="D37" s="3">
+        <v>1905.2652479999999</v>
+      </c>
+      <c r="E37" s="3">
+        <v>768.4297439999998</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B9">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:C9">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D9">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E9">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13:B20">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -913,8 +1072,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C9">
-    <cfRule type="colorScale" priority="7">
+  <conditionalFormatting sqref="B34:B37">
+    <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -925,8 +1084,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D9">
-    <cfRule type="colorScale" priority="6">
+  <conditionalFormatting sqref="C34:C37">
+    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -937,8 +1096,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E9">
-    <cfRule type="colorScale" priority="5">
+  <conditionalFormatting sqref="D34:D37">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -949,8 +1108,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B13:B20">
-    <cfRule type="colorScale" priority="4">
+  <conditionalFormatting sqref="E34:E37">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
